--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/magallanes-y-antartica.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/magallanes-y-antartica.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>5339.24</v>
+        <v>5279.76</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2297.75</v>
+        <v>2322.74</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3648.96</v>
+        <v>3642.49</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>6412.33</v>
+        <v>6402.39</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>5247.68</v>
+        <v>5274.79</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1852.39</v>
+        <v>1861.96</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2613.07</v>
+        <v>2579.88</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>24549.71</v>
+        <v>24237.87</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3359.66</v>
+        <v>3320.78</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2888.24</v>
+        <v>2854.81</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2586.54</v>
+        <v>2598.27</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>545.75</v>
+        <v>549.51</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>7673.37</v>
+        <v>7493.87</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2758.93</v>
+        <v>2719.18</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>5656.33</v>
+        <v>5664.18</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1357.52</v>
+        <v>1359.4</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>65148.32</v>
+        <v>66140.14</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>8952.27</v>
+        <v>9223.73</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>76859.58</v>
+        <v>77365.77</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2320.13</v>
+        <v>2316.72</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>6166</v>
+        <v>6197.92</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3512.47</v>
+        <v>3430.73</v>
       </c>
     </row>
     <row r="24">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>120069.04</v>
+        <v>117275.14</v>
       </c>
     </row>
     <row r="25">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>3591.37</v>
+        <v>3598.81</v>
       </c>
     </row>
     <row r="26">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>157.41</v>
+        <v>158.59</v>
       </c>
     </row>
     <row r="27">
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1002.63</v>
+        <v>991.72</v>
       </c>
     </row>
     <row r="28">
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>19658.82</v>
+        <v>19610.27</v>
       </c>
     </row>
     <row r="29">
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>64156.02</v>
+        <v>64360.21</v>
       </c>
     </row>
     <row r="30">
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>6989.09</v>
+        <v>6893.06</v>
       </c>
     </row>
     <row r="31">
@@ -2342,7 +2342,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2939.6</v>
+        <v>2959.89</v>
       </c>
     </row>
     <row r="32">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>8958.77</v>
+        <v>9020.620000000001</v>
       </c>
     </row>
     <row r="33">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1771.12</v>
+        <v>1744.88</v>
       </c>
     </row>
     <row r="34">
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>15433.37</v>
+        <v>15399.79</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/magallanes-y-antartica.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/magallanes-y-antartica.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1000813-459-CM25</t>
+          <t>5020-28-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.999.040-4</t>
+          <t>65.940.830-9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>5279.76</v>
+        <v>4113.42</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3229-10200-CM25</t>
+          <t>707427-26-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.102.026-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA IIIa ZONA NAVAL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2322.74</v>
+        <v>53597.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1057402-43349-CM25</t>
+          <t>935-5820-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3642.49</v>
+        <v>607.08</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1965-741-CM25</t>
+          <t>5020-65-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.004.054-3</t>
+          <t>65.940.830-9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Pta. Arenas</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>6402.39</v>
+        <v>7258.68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5221-147-CM25</t>
+          <t>829-25-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.607.900-k</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>5274.79</v>
+        <v>426.92</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3367-159-CM25</t>
+          <t>1965-485-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.927.400-8</t>
+          <t>61.004.054-3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1861.96</v>
+        <v>860.1900000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3407-324-CM25</t>
+          <t>1965-684-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.101.470-8</t>
+          <t>61.004.054-3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2579.88</v>
+        <v>6690.53</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1609-419-CM25</t>
+          <t>1000813-459-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>72.229.800-4</t>
+          <t>61.999.040-4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
+          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>24237.87</v>
+        <v>5279.76</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3412-246-CM25</t>
+          <t>3229-10200-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,27 +1012,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.101.080-K</t>
+          <t>61.102.026-0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>COMANDANCIA EN JEFE DE LA IIIa ZONA NAVAL</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>3320.78</v>
+        <v>2322.74</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3229-10368-CM25</t>
+          <t>1057402-43349-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.102.026-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA IIIa ZONA NAVAL</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2854.81</v>
+        <v>3642.49</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4305-202-CM25</t>
+          <t>1965-741-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.943.400-5</t>
+          <t>61.004.054-3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Dirección Regional de Gendarmeria - Pta. Arenas</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2598.27</v>
+        <v>6402.39</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3617-262-CM25</t>
+          <t>5221-147-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.607.900-k</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>549.51</v>
+        <v>5274.79</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1965-811-CM25</t>
+          <t>3367-159-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.004.054-3</t>
+          <t>61.927.400-8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Pta. Arenas</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>7493.87</v>
+        <v>1861.96</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1057402-45096-CM25</t>
+          <t>3407-324-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.101.470-8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2719.18</v>
+        <v>2579.88</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4305-3-CM26</t>
+          <t>1609-419-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.943.400-5</t>
+          <t>72.229.800-4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>5664.18</v>
+        <v>24237.87</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4305-4-CM26</t>
+          <t>3229-10368-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,27 +1439,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.943.400-5</t>
+          <t>61.102.026-0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>COMANDANCIA EN JEFE DE LA IIIa ZONA NAVAL</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1359.4</v>
+        <v>2854.81</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3233-1-CM26</t>
+          <t>3412-246-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,27 +1500,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.102.026-0</t>
+          <t>61.101.080-K</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA IIIa ZONA NAVAL</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>66140.14</v>
+        <v>3320.78</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1965-47-CM26</t>
+          <t>4305-202-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.004.054-3</t>
+          <t>61.943.400-5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Pta. Arenas</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>9223.73</v>
+        <v>2598.27</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>707427-9-CM26</t>
+          <t>3617-262-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>77365.77</v>
+        <v>549.51</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3409-30-CM26</t>
+          <t>1965-811-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.101.455-4</t>
+          <t>61.004.054-3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Dirección Regional de Gendarmeria - Pta. Arenas</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2316.72</v>
+        <v>7493.87</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1057402-2360-CM26</t>
+          <t>1057402-45096-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>6197.92</v>
+        <v>2719.18</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>707427-17-CM26</t>
+          <t>4305-3-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,27 +1805,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.943.400-5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3430.73</v>
+        <v>5664.18</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>517903-28-CM26</t>
+          <t>4305-4-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.114.000-2</t>
+          <t>61.943.400-5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>EMDN-RMA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1904,24 +1904,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>117275.14</v>
+        <v>1359.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1057402-4750-CM26</t>
+          <t>3233-1-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1931,27 +1927,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.026-0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>COMANDANCIA EN JEFE DE LA IIIa ZONA NAVAL</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1976,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>3598.81</v>
+        <v>66140.14</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3367-44-CM26</t>
+          <t>1965-47-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1992,12 +1988,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2007,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.927.400-8</t>
+          <t>61.004.054-3</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>Dirección Regional de Gendarmeria - Pta. Arenas</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2037,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>158.59</v>
+        <v>9223.73</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3407-111-CM26</t>
+          <t>707427-9-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2053,27 +2049,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.101.470-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2098,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>991.72</v>
+        <v>77365.77</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4305-68-CM26</t>
+          <t>3409-30-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2114,12 +2110,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2129,7 +2125,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.943.400-5</t>
+          <t>61.101.455-4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2159,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>19610.27</v>
+        <v>2316.72</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3233-28-CM26</t>
+          <t>1057402-2360-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2175,27 +2171,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.102.026-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>COMANDANCIA EN JEFE DE LA IIIa ZONA NAVAL</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2220,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>64360.21</v>
+        <v>6197.92</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1288505-81-CM26</t>
+          <t>517903-28-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2236,12 +2232,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2251,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.114.000-2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL DE MAGALLANES</t>
+          <t>EMDN-RMA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2274,20 +2270,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>6893.06</v>
+        <v>117275.14</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1057402-6715-CM26</t>
+          <t>707427-17-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2297,27 +2297,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2342,13 +2342,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>2959.89</v>
+        <v>3430.73</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1057402-6716-CM26</t>
+          <t>1057402-4750-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2403,28 +2403,28 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>9020.620000000001</v>
+        <v>3598.81</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1000813-270-CM26</t>
+          <t>3367-44-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.999.040-4</t>
+          <t>61.927.400-8</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2464,28 +2464,28 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1744.88</v>
+        <v>158.59</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5020-81-CM26</t>
+          <t>3407-111-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>65.940.830-9</t>
+          <t>61.101.470-8</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2525,6 +2525,433 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
+        <v>991.72</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>4305-68-CM26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>61.943.400-5</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>19610.27</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>3233-28-CM26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>61.102.026-0</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>COMANDANCIA EN JEFE DE LA IIIa ZONA NAVAL</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>64360.21</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1288505-81-CM26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>60.905.000-4</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>DIRECCIÓN REGIONAL DE MAGALLANES</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>6893.06</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1057402-6715-CM26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>2959.89</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1057402-6716-CM26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>61.607.901-8</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>9020.620000000001</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1000813-270-CM26</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>61.999.040-4</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>1744.88</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>5020-81-CM26</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>65.940.830-9</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Magallanes y Antártica</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
         <v>15399.79</v>
       </c>
     </row>
